--- a/test-real-data/tiempos_transporte.xlsx
+++ b/test-real-data/tiempos_transporte.xlsx
@@ -122,8 +122,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -320,319 +324,319 @@
   <sheetFormatPr defaultColWidth="9.11328125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>6.71666666666666</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>5.73888888888889</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>6.13333333333333</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>7.58888888888889</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="1" t="n">
         <v>4.56666666666667</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="G2" s="1" t="n">
         <v>5.88333333333333</v>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2" s="1" t="n">
         <v>11.3166666666666</v>
       </c>
-      <c r="I2" s="0" t="n">
+      <c r="I2" s="1" t="n">
         <v>5.7</v>
       </c>
-      <c r="J2" s="0" t="n">
+      <c r="J2" s="1" t="n">
         <v>9.56666666666666</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>4.78611111111111</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>4.10833333333333</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>4.60277777777777</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>6.625</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="1" t="n">
         <v>3.9</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="G3" s="1" t="n">
         <v>7.87222222222222</v>
       </c>
-      <c r="H3" s="0" t="n">
+      <c r="H3" s="1" t="n">
         <v>13.3166666666666</v>
       </c>
-      <c r="I3" s="0" t="n">
+      <c r="I3" s="1" t="n">
         <v>5.12222222222222</v>
       </c>
-      <c r="J3" s="0" t="n">
+      <c r="J3" s="1" t="n">
         <v>11.6111111111111</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>2.64999999999999</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>3.20555555555555</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>4.78333333333333</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <v>5.72222222222222</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <v>5.21666666666667</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4" s="1" t="n">
         <v>10.1611111111111</v>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4" s="1" t="n">
         <v>15.6055555555555</v>
       </c>
-      <c r="I4" s="0" t="n">
+      <c r="I4" s="1" t="n">
         <v>7.34999999999999</v>
       </c>
-      <c r="J4" s="0" t="n">
+      <c r="J4" s="1" t="n">
         <v>13.8444444444444</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>6.43333333333333</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <v>4.85</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <v>8.55</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <v>2.43333333333333</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <v>1.08333333333333</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="G5" s="1" t="n">
         <v>9.3</v>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="H5" s="1" t="n">
         <v>14.7333333333333</v>
       </c>
-      <c r="I5" s="0" t="n">
+      <c r="I5" s="1" t="n">
         <v>10.0666666666666</v>
       </c>
-      <c r="J5" s="0" t="n">
+      <c r="J5" s="1" t="n">
         <v>12.9666666666666</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>4.73541666666666</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="1" t="n">
         <v>3.16458333333333</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <v>6.86458333333333</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1" t="n">
         <v>1.97291666666666</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="1" t="n">
         <v>3.46666666666667</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6" s="1" t="n">
         <v>13.1520833333333</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6" s="1" t="n">
         <v>12.8916666666667</v>
       </c>
-      <c r="I6" s="0" t="n">
+      <c r="I6" s="1" t="n">
         <v>10.5979166666667</v>
       </c>
-      <c r="J6" s="0" t="n">
+      <c r="J6" s="1" t="n">
         <v>16.8770833333333</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>5.75</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="1" t="n">
         <v>4.18333333333333</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <v>7.88333333333333</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="1" t="n">
         <v>1.2</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <v>3.21666666666667</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="G7" s="1" t="n">
         <v>11.25</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7" s="1" t="n">
         <v>9.8125</v>
       </c>
-      <c r="I7" s="0" t="n">
+      <c r="I7" s="1" t="n">
         <v>11.55</v>
       </c>
-      <c r="J7" s="0" t="n">
+      <c r="J7" s="1" t="n">
         <v>14.9333333333333</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>6.64444444444444</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="1" t="n">
         <v>8.33333333333333</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <v>5.53333333333333</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="1" t="n">
         <v>10.85</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="1" t="n">
         <v>8.88333333333333</v>
       </c>
-      <c r="G8" s="0" t="n">
+      <c r="G8" s="1" t="n">
         <v>12.1888888888889</v>
       </c>
-      <c r="H8" s="0" t="n">
+      <c r="H8" s="1" t="n">
         <v>17.65</v>
       </c>
-      <c r="I8" s="0" t="n">
+      <c r="I8" s="1" t="n">
         <v>1.31666666666667</v>
       </c>
-      <c r="J8" s="0" t="n">
+      <c r="J8" s="1" t="n">
         <v>7.65</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <v>4.66666666666666</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="1" t="n">
         <v>6.36666666666666</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <v>3.56666666666666</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="1" t="n">
         <v>8.88333333333333</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9" s="1" t="n">
         <v>7.3</v>
       </c>
-      <c r="G9" s="0" t="n">
+      <c r="G9" s="1" t="n">
         <v>10.0666666666666</v>
       </c>
-      <c r="H9" s="0" t="n">
+      <c r="H9" s="1" t="n">
         <v>15.5</v>
       </c>
-      <c r="I9" s="0" t="n">
+      <c r="I9" s="1" t="n">
         <v>1.6</v>
       </c>
-      <c r="J9" s="0" t="n">
+      <c r="J9" s="1" t="n">
         <v>8.83333333333333</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="1" t="n">
         <v>6.08333333333333</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="1" t="n">
         <v>7.76666666666666</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="1" t="n">
         <v>4.63333333333333</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10" s="1" t="n">
         <v>10.3</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="1" t="n">
         <v>8.81666666666667</v>
       </c>
-      <c r="G10" s="0" t="n">
+      <c r="G10" s="1" t="n">
         <v>11.9333333333333</v>
       </c>
-      <c r="H10" s="0" t="n">
+      <c r="H10" s="1" t="n">
         <v>17.3666666666666</v>
       </c>
-      <c r="I10" s="0" t="n">
+      <c r="I10" s="1" t="n">
         <v>0.616666666666666</v>
       </c>
-      <c r="J10" s="0" t="n">
+      <c r="J10" s="1" t="n">
         <v>8.66666666666666</v>
       </c>
     </row>
